--- a/Result/profitability/8033.xlsx
+++ b/Result/profitability/8033.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>0.12</v>
+        <v>0.18125</v>
       </c>
       <c r="N2" t="n">
-        <v>38.65875</v>
+        <v>37.90125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1525</v>
+        <v>0.16</v>
       </c>
       <c r="N3" t="n">
-        <v>38.93625</v>
+        <v>38.91</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.23</v>
       </c>
       <c r="M4" t="n">
-        <v>0.15375</v>
+        <v>0.1575</v>
       </c>
       <c r="N4" t="n">
-        <v>40.00125</v>
+        <v>39.55500000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.10125</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>40.76875</v>
+        <v>40.3175</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>41.32125</v>
+        <v>41.42</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05750000000000001</v>
+        <v>0.11125</v>
       </c>
       <c r="N7" t="n">
-        <v>42.08</v>
+        <v>42.0425</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.03250000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>42.58125</v>
+        <v>42.2475</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>-0.09625</v>
       </c>
       <c r="N10" t="n">
-        <v>41.90000000000001</v>
+        <v>41.9</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>-0.225</v>
       </c>
       <c r="N12" t="n">
-        <v>40.2575</v>
+        <v>40.25750000000001</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8033</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>464</v>
+      </c>
+      <c r="D75" t="n">
+        <v>299</v>
+      </c>
+      <c r="E75" t="n">
+        <v>165</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.10%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>44</v>
+      </c>
+      <c r="J75" t="n">
+        <v>44</v>
+      </c>
+      <c r="K75" t="n">
+        <v>44</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>37.49375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.176470588235294</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.670000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06987699555090299</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3777777777777778</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.609999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.09220945083014043</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
